--- a/data/flo/invoice-numbers.xlsx
+++ b/data/flo/invoice-numbers.xlsx
@@ -24,13 +24,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +47,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -55,14 +68,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -379,34 +392,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
-        <v>1010033788</v>
+        <v>1010050331</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2">
-        <v>1010033791</v>
+        <v>1010050332</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="2">
-        <v>1010033790</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="2">
-        <v>1010033792</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="2">
-        <v>1010033776</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="1"/>
+      <c r="A7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
